--- a/fo76_special_reference.xlsx
+++ b/fo76_special_reference.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Perk Cards'!$A$4:$F$247</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Legendary Effects'!$A$3:$G$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Legendary Perks'!$A$4:$F$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Mechanics &amp; Caps'!$A$3:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Mechanics &amp; Caps'!$A$3:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Perk Values'!$A$4:$P$247</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Legendary Values'!$A$4:$F$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Presets'!$A$4:$IQ$6</definedName>
@@ -12920,7 +12920,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Impairment Types on Target (0-5)</t>
+          <t>Impairment Types on Target (0-5; Deal Sealer caps at 4)</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -12954,7 +12954,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Onslaught Stacks Right Now (0-30)</t>
+          <t>Onslaught Stacks Right Now (standard builds cap ~20; 30 needs reverse Onslaught)</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -13739,11 +13739,11 @@
         </is>
       </c>
       <c r="B70" s="7">
-        <f>$B$27*IF($B$6&gt;0,1,0)+$B$28*$B$6+$B$30*$B$7+$B$31*MIN($B$12,20)*IF($B$16="Y",1,0)+$B$37*$B$10*IF($B$14="Y",1,0)+$B$35*IF($B$14="Y",1,0)+$B$38*MIN($B$11,10)+$B$13/100+$B$43*IF($B$20="Y",1,0)+$B$44*IF($B$8="Y",1,0)+$B$32*B77+$B$46*IF($B$15&gt;=47,1,0)+$B$47*(1-$B$17/100)+B62</f>
+        <f>$B$27*IF($B$6&gt;0,1,0)+$B$28*$B$6+$B$30*MIN($B$7,4)+$B$31*MIN($B$12,20)*IF($B$16="Y",1,0)+$B$37*$B$10*IF($B$14="Y",1,0)+$B$35*IF($B$14="Y",1,0)+$B$38*MIN($B$11,10)+$B$13/100+$B$43*IF($B$20="Y",1,0)+$B$44*IF($B$8="Y",1,0)+$B$32*B77+$B$46*IF($B$15&gt;=47,1,0)+$B$47*(1-$B$17/100)+B62</f>
         <v/>
       </c>
       <c r="C70" s="7">
-        <f>$B$27*IF($B$6&gt;0,1,0)+$B$28*$B$6+$B$30*$B$7+$B$31*MIN($B$12,20)*IF($B$16="Y",1,0)+$B$37*$B$10*IF($B$14="Y",1,0)+$B$35*IF($B$14="Y",1,0)+$B$38*MIN($B$11,10)+$B$13/100+$B$43*IF($B$20="Y",1,0)+$B$44*IF($B$8="Y",1,0)+$B$32*C77+$B$46*IF($B$15&gt;=47,1,0)+$B$47*(1-$B$17/100)+C62</f>
+        <f>$B$27*IF($B$6&gt;0,1,0)+$B$28*$B$6+$B$30*MIN($B$7,4)+$B$31*MIN($B$12,20)*IF($B$16="Y",1,0)+$B$37*$B$10*IF($B$14="Y",1,0)+$B$35*IF($B$14="Y",1,0)+$B$38*MIN($B$11,10)+$B$13/100+$B$43*IF($B$20="Y",1,0)+$B$44*IF($B$8="Y",1,0)+$B$32*C77+$B$46*IF($B$15&gt;=47,1,0)+$B$47*(1-$B$17/100)+C62</f>
         <v/>
       </c>
       <c r="D70" s="7">
@@ -24026,7 +24026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -24441,27 +24441,115 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
+          <t>Patch currency of this workbook</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Latest content update is The Slasher (Patch 70, Sept 15 2026). A hotfix followed on Oct 1 2026 but it was stability-only (PlayStation/Xbox crash fixes, plus a unique-appearance fix for Head Hunter Scythe / Cauterizer / Drill Fist) with NO balance or perk changes. Nothing shipped between that hotfix and this workbook's build date, so every number here reflects live Patch 70 values.</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Bethesda - The Slasher release notes; nukaknights.com Patch 70 hotfix notice; Fallout Wiki updates list</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Impairment TYPES vs crippled LIMBS — don't double-count</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Deal Sealer counts impairment TYPES (bleeding, burning, crippled, poisoned, and cryo/freezing which was added after launch) and caps at +40%, i.e. 4 types' worth. Critically, several crippled limbs still count as only ONE impairment for Deal Sealer. Tormentor (+20%) and the Bully's legendary (+25%) are the opposite — they scale per crippled LIMB. The Weapon Comparison sheet models this correctly: Deal Sealer uses MIN(impairment types, 4), while Tormentor and Bully's multiply by the crippled-limb count.</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Fallout 76 Wiki - Deal Sealer; Bethesda developer notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Don't trust PTS previews for live numbers</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Bethesda's June 2025 'upcoming combat and perk changes' article is the primary source for the big rework, but several of its values changed before shipping: the heavy-gun perk was previewed as 'Drum Corps' granting 1 stack per 50 ammo and shipped as 'Bullet Storm' at 1 stack per 30 ammo; Knee-Capper previewed at +100% limb damage and shipped nearer +50%; Psychopath previewed as 3 ranks and shipped as 1. Where a PTS preview and a post-ship source disagree, this workbook uses the post-ship value.</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Bethesda - Inside the Vault (June 27 2025) compared against post-ship wiki/changelog values</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Enemy resistances were raised in the same rework</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>The combat rework also increased health and/or resistances for Super Mutants, Power Armor enemies, Scorchbeasts, Deathclaws, Mirelurks and turrets, and deliberately widened resistance contrast between damage types. Enemy DR figures quoted in pre-rework build guides are therefore stale — pull the 'Enemy Base Damage Resistance' input from current creature data rather than an older guide.</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Bethesda - Inside the Vault (June 27 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
           <t>A second research pass corrected several numbers</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Better Criticals was reworked from 20/30/40% to 50/75/100% by patch 1.6.4.60 and this workbook had the stale pre-rework number until a second pass caught it. Glowing Criticals turned out to be 3 ranks (20/35/50%), not a single flat 50%. Ironclad is a clean 15/20/25% per rank (doubled to 30/40/50% with a 5-piece set), not '+15% then +2% per rank after.' Gunslinger Expert, Guerrilla Expert, Guerrilla Master, Awareness, Adrenaline, and Life Giver are each single-rank, higher-point-cost cards, not multi-rank cards — the point cost was already right, only the displayed rank number was corrected.</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>second independent research pass this session, cross-verified against individual wiki pages</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D21"/>
+  <autoFilter ref="A3:D25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
